--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_04-05-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_04-05-2026.xlsx
@@ -533,17 +533,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>£14.50</t>
+          <t>£14.75</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>£14.50</t>
+          <t>£14.75</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>£14.50</t>
+          <t>£14.75</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>£27.67</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>POA</t>
+          <t>£1189.4</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>£76.11</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Read timed out. (read timeout=30)</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>POA</t>
+          <t>£1853.87</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
